--- a/data/S2007_08_FINAL.xlsx
+++ b/data/S2007_08_FINAL.xlsx
@@ -26,8 +26,11 @@
     <sheet name="SERIES" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="CLUBS" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="META" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -35,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +75,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -81,11 +93,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -10931,7 +10949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10975,6 +10993,93 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2007_08_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2007_08_0032 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2007_08_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0021</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2007_08_0021 'Baráž o Extraligu' (L15, parent=NODE_S2007_08_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0028</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2007_08_0028 'Baráž o I.ligu' (L25, parent=NODE_S2007_08_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0041</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2007_08_0041 'O postup do I.ligy' (L25, parent=NODE_S2007_08_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -14105,8 +14210,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -14186,7 +14289,6 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -28261,6 +28363,193 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0031</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0032</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0032 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0033</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0021</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2007_08_0021 'Baráž o Extraligu' (L15, parent=NODE_S2007_08_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0028</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2007_08_0028 'Baráž o I.ligu' (L25, parent=NODE_S2007_08_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0041</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2007_08_0041 'O postup do I.ligy' (L25, parent=NODE_S2007_08_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2007_08_FINAL.xlsx
+++ b/data/S2007_08_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10949,7 +10949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10999,7 +10999,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2007_08_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11011,7 +11011,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2007_08_0032 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11023,7 +11023,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2007_08_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11033,14 +11033,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S2007_08_0021</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2007_08_0021 'Baráž o Extraligu' (L15, parent=NODE_S2007_08_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11050,14 +11045,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S2007_08_0028</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2007_08_0028 'Baráž o I.ligu' (L25, parent=NODE_S2007_08_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -11067,17 +11057,346 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S2007_08_0041</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2007_08_0041 'O postup do I.ligy' (L25, parent=NODE_S2007_08_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2006_07_0135 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Mariánské Lázně' → 'Farmáři Trstěnice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0030</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0031</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -14210,6 +14529,8 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -14240,6 +14561,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0001</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -14252,6 +14578,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0003</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -14264,6 +14595,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0003</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -14276,6 +14612,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0035</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -14289,6 +14630,7 @@
         </is>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -18040,12 +18382,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -18292,12 +18634,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -18633,12 +18975,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -18675,12 +19017,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -18717,12 +19059,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -18806,12 +19148,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň.</t>
+          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň. || TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Sportovní klub Kadaň</t>
+          <t>Kadaň</t>
         </is>
       </c>
     </row>
@@ -19399,12 +19741,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno.</t>
+          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno. || TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>VSK Technika Brno</t>
+          <t>Technika Brno</t>
         </is>
       </c>
     </row>
@@ -20110,12 +20452,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -20236,12 +20578,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -20535,12 +20877,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný.</t>
+          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný. || TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>UHK LEV Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -20656,12 +20998,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Tábor = Hockey Club Tábor (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. city Tábor.</t>
+          <t>Tábor = Hockey Club Tábor (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. city Tábor. || TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Hockey Club Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -20735,12 +21077,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk.</t>
+          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk. || TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
@@ -20861,12 +21203,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>SC Kolín</t>
         </is>
       </c>
     </row>
@@ -20903,12 +21245,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -21706,12 +22048,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -22299,12 +22641,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -22425,12 +22767,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -23065,12 +23407,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Mariánské Lázně (Wiki - registr ustavy 04/2026). Zapadocesky/Karlovarsky kraj. - hokej tradice mensi. city Mariánské Lázně.</t>
+          <t>Mariánské Lázně (Wiki - registr ustavy 04/2026). Zapadocesky/Karlovarsky kraj. - hokej tradice mensi. city Mariánské Lázně. || TBD: city 'Mariánské Lázně' → 'Farmáři Trstěnice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Mariánské Lázně</t>
+          <t>Farmáři Trstěnice</t>
         </is>
       </c>
     </row>
@@ -23322,12 +23664,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -23868,12 +24210,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -24083,12 +24425,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka.</t>
+          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka. || TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>BK JTC Nová Paka</t>
+          <t>Nová Paka</t>
         </is>
       </c>
     </row>
@@ -24382,12 +24724,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou.</t>
+          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou. || TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>SB Světlá nad Sázavou</t>
+          <t>Světlá nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -24955,12 +25297,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -25412,12 +25754,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Brno = HLC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: HLC Brno + Bulldogs Brno. city Brno.</t>
+          <t>Brno = HLC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: HLC Brno + Bulldogs Brno. city Brno. || TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>HLC Bulldogs Brno</t>
+          <t>Bulldogs Brno</t>
         </is>
       </c>
     </row>
@@ -25659,12 +26001,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -28369,11 +28711,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -28418,21 +28760,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0031</t>
+          <t>CLUB_S2007_08_0001</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -28440,21 +28780,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0032</t>
+          <t>CLUB_S2007_08_0007</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0032 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -28462,21 +28800,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0033</t>
+          <t>CLUB_S2007_08_0015</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -28484,21 +28820,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S2007_08_0021</t>
+          <t>CLUB_S2007_08_0016</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2007_08_0021 'Baráž o Extraligu' (L15, parent=NODE_S2007_08_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -28506,21 +28840,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S2007_08_0028</t>
+          <t>CLUB_S2007_08_0017</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2007_08_0028 'Baráž o I.ligu' (L25, parent=NODE_S2007_08_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -28528,24 +28860,562 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S2007_08_0041</t>
+          <t>CLUB_S2007_08_0019</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2007_08_0041 'O postup do I.ligy' (L25, parent=NODE_S2007_08_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0033</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0053</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2006_07_0135 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0054</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0057</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0064</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0069</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0071</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0074</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0095</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0109</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0109</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0112</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0123</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0127</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Mariánské Lázně' → 'Farmáři Trstěnice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0134</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0145</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0147</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0153</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0160</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0162</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0174</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0176</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0187</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0195</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0030</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0031</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2007_08_FINAL.xlsx
+++ b/data/S2007_08_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10949,7 +10949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10999,7 +10999,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11011,7 +11011,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11023,7 +11023,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11035,7 +11035,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11047,7 +11047,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2006_07_0135 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -11059,7 +11059,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -11071,7 +11071,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -11083,7 +11083,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2006_07_0135 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -11095,7 +11095,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -11107,7 +11107,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -11119,7 +11119,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -11131,7 +11131,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -11143,7 +11143,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11155,7 +11155,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11167,7 +11167,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11179,7 +11179,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11191,7 +11191,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -11203,7 +11203,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -11215,7 +11215,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -11227,7 +11227,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -11239,7 +11239,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Mariánské Lázně' → 'Farmáři Trstěnice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -11249,9 +11249,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0030</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -11261,142 +11266,17 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0031</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NODE_S2007_08_0030</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>NODE_S2007_08_0031</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -11413,7 +11293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11472,6 +11352,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11514,6 +11399,11 @@
           <t>14 týmů (5 stat sloupců): základ + QF/SF/finále + baráž. Mistr: HC Slavia Praha.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11561,6 +11451,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11603,6 +11498,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11645,6 +11545,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11687,6 +11592,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11729,6 +11639,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11771,6 +11686,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11813,6 +11733,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11855,6 +11780,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11897,6 +11827,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11939,6 +11874,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11981,6 +11921,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12023,6 +11968,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12065,6 +12015,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12107,6 +12062,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12149,6 +12109,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12191,6 +12156,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12233,6 +12203,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12275,6 +12250,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12317,6 +12297,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12359,6 +12344,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12401,6 +12391,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12443,6 +12438,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12485,6 +12485,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12527,6 +12532,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12569,6 +12579,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12611,6 +12626,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12653,6 +12673,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12700,6 +12725,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12806,6 +12836,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0030</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -12932,6 +12967,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0033</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12974,6 +13014,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0034</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13016,6 +13061,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0035</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13058,6 +13108,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0036</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13100,6 +13155,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0037</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13142,6 +13202,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0038</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -13184,6 +13249,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0039</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -13226,6 +13296,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0040</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -13268,6 +13343,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0041</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -13310,6 +13390,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0042</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -13352,6 +13437,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0043</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13394,6 +13484,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0044</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -13436,6 +13531,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0045</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -13478,6 +13578,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0048</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -13562,6 +13667,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0049</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -13688,6 +13798,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0050</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -13814,6 +13929,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0055</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13898,6 +14018,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0057</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -14150,6 +14275,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0063</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -14192,6 +14322,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0064</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -14234,6 +14369,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0066</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -14276,6 +14416,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0067</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -14318,6 +14463,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0067</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -14360,6 +14510,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0071</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -14402,6 +14557,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0072</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -14526,6 +14686,11 @@
       <c r="K74" t="inlineStr">
         <is>
           <t>Kontejner L40</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S2006_07_0075</t>
         </is>
       </c>
     </row>
@@ -14549,6 +14714,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -14566,6 +14736,11 @@
           <t>NODE_S2007_08_0001</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -14583,6 +14758,11 @@
           <t>NODE_S2007_08_0003</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -14600,6 +14780,11 @@
           <t>NODE_S2007_08_0003</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -14617,6 +14802,11 @@
           <t>NODE_S2007_08_0035</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -14627,6 +14817,11 @@
       <c r="B83" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -18382,12 +18577,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -18975,12 +19170,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -19059,12 +19254,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -21203,12 +21398,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>SC Kolín</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -22048,12 +22243,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -22641,12 +22836,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -22767,12 +22962,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -23407,12 +23602,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Mariánské Lázně (Wiki - registr ustavy 04/2026). Zapadocesky/Karlovarsky kraj. - hokej tradice mensi. city Mariánské Lázně. || TBD: city 'Mariánské Lázně' → 'Farmáři Trstěnice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Mariánské Lázně (Wiki - registr ustavy 04/2026). Zapadocesky/Karlovarsky kraj. - hokej tradice mensi. city Mariánské Lázně.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Farmáři Trstěnice</t>
+          <t>Mariánské Lázně</t>
         </is>
       </c>
     </row>
@@ -25297,12 +25492,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -26001,12 +26196,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
@@ -28711,7 +28906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -28765,12 +28960,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0001</t>
+          <t>CLUB_S2007_08_0007</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28785,12 +28980,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0007</t>
+          <t>CLUB_S2007_08_0016</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28805,12 +29000,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0015</t>
+          <t>CLUB_S2007_08_0019</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28825,12 +29020,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0016</t>
+          <t>CLUB_S2007_08_0033</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28845,12 +29040,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0017</t>
+          <t>CLUB_S2007_08_0053</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2006_07_0135 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -28865,12 +29060,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0019</t>
+          <t>CLUB_S2007_08_0054</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28885,12 +29080,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0033</t>
+          <t>CLUB_S2007_08_0057</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28905,12 +29100,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0053</t>
+          <t>CLUB_S2007_08_0064</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2006_07_0135 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28925,12 +29120,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0054</t>
+          <t>CLUB_S2007_08_0069</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28945,12 +29140,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0057</t>
+          <t>CLUB_S2007_08_0071</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28965,12 +29160,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0064</t>
+          <t>CLUB_S2007_08_0075</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28985,12 +29180,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0069</t>
+          <t>CLUB_S2007_08_0109</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29005,12 +29200,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0071</t>
+          <t>CLUB_S2007_08_0123</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -29025,12 +29220,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0074</t>
+          <t>CLUB_S2007_08_0134</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29045,12 +29240,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0075</t>
+          <t>CLUB_S2007_08_0145</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -29065,12 +29260,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0095</t>
+          <t>CLUB_S2007_08_0147</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29085,12 +29280,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0109</t>
+          <t>CLUB_S2007_08_0153</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29105,12 +29300,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0109</t>
+          <t>CLUB_S2007_08_0160</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29125,12 +29320,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0112</t>
+          <t>CLUB_S2007_08_0162</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -29145,12 +29340,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0123</t>
+          <t>CLUB_S2007_08_0174</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -29165,12 +29360,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0127</t>
+          <t>CLUB_S2007_08_0187</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Mariánské Lázně' → 'Farmáři Trstěnice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -29180,17 +29375,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0134</t>
+          <t>NODE_S2007_08_0030</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
     </row>
@@ -29200,222 +29395,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S2007_08_0145</t>
+          <t>NODE_S2007_08_0031</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CLUB_S2007_08_0147</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CLUB_S2007_08_0153</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CLUB_S2007_08_0160</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CLUB_S2007_08_0162</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CLUB_S2007_08_0174</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLUB_S2007_08_0176</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CLUB_S2007_08_0187</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S2007_08_0195</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>NODE_S2007_08_0030</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>NODE_S2007_08_0031</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F34"/>
+  <autoFilter ref="A1:F24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2007_08_FINAL.xlsx
+++ b/data/S2007_08_FINAL.xlsx
@@ -11293,7 +11293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11357,6 +11357,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14694,8 +14704,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -14825,7 +14833,6 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>

--- a/data/S2007_08_FINAL.xlsx
+++ b/data/S2007_08_FINAL.xlsx
@@ -11545,6 +11545,16 @@
           <t>NODE_S2007_08_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11559,6 +11569,14 @@
         <is>
           <t>NODE_S2006_07_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -11733,6 +11751,16 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11747,6 +11775,14 @@
         <is>
           <t>NODE_S2006_07_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -11827,6 +11863,16 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11841,6 +11887,14 @@
         <is>
           <t>NODE_S2006_07_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1.–10. ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -11874,6 +11928,16 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11888,6 +11952,14 @@
         <is>
           <t>NODE_S2006_07_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -11921,6 +11993,8 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11935,6 +12009,14 @@
         <is>
           <t>NODE_S2006_07_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -11968,6 +12050,8 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11982,6 +12066,14 @@
         <is>
           <t>NODE_S2006_07_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -12015,6 +12107,8 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12029,6 +12123,14 @@
         <is>
           <t>NODE_S2006_07_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -12062,6 +12164,8 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12076,6 +12180,14 @@
         <is>
           <t>NODE_S2006_07_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -12109,6 +12221,8 @@
           <t>NODE_S2007_08_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12123,6 +12237,14 @@
         <is>
           <t>NODE_S2006_07_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>11.–14. ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -12156,6 +12278,8 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12170,6 +12294,14 @@
         <is>
           <t>NODE_S2006_07_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -12203,6 +12335,8 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12217,6 +12351,14 @@
         <is>
           <t>NODE_S2006_07_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -12250,6 +12392,16 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12264,6 +12416,14 @@
         <is>
           <t>NODE_S2006_07_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -12391,6 +12551,16 @@
           <t>NODE_S2007_08_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12405,6 +12575,14 @@
         <is>
           <t>NODE_S2006_07_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -12438,6 +12616,16 @@
           <t>NODE_S2007_08_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12452,6 +12640,14 @@
         <is>
           <t>NODE_S2006_07_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -12485,6 +12681,12 @@
           <t>NODE_S2007_08_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12499,6 +12701,14 @@
         <is>
           <t>NODE_S2006_07_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -12532,6 +12742,12 @@
           <t>NODE_S2007_08_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12546,6 +12762,14 @@
         <is>
           <t>NODE_S2006_07_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -12579,6 +12803,8 @@
           <t>NODE_S2007_08_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12593,6 +12819,14 @@
         <is>
           <t>NODE_S2006_07_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -12626,6 +12860,8 @@
           <t>NODE_S2007_08_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12640,6 +12876,14 @@
         <is>
           <t>NODE_S2006_07_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -13108,6 +13352,12 @@
           <t>NODE_S2007_08_0035</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0039</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13122,6 +13372,14 @@
         <is>
           <t>NODE_S2006_07_0036</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -13155,6 +13413,12 @@
           <t>NODE_S2007_08_0035</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0040</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13169,6 +13433,14 @@
         <is>
           <t>NODE_S2006_07_0037</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -13202,6 +13474,8 @@
           <t>NODE_S2007_08_0035</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13216,6 +13490,14 @@
         <is>
           <t>NODE_S2006_07_0038</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -13343,6 +13625,8 @@
           <t>NODE_S2007_08_0035</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13357,6 +13641,14 @@
         <is>
           <t>NODE_S2006_07_0041</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -13484,6 +13776,12 @@
           <t>NODE_S2007_08_0035</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0038</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13498,6 +13796,14 @@
         <is>
           <t>NODE_S2006_07_0044</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -13625,6 +13931,12 @@
           <t>NODE_S2007_08_0048</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0050</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13634,6 +13946,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -13667,6 +13987,8 @@
           <t>NODE_S2007_08_0048</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13681,6 +14003,14 @@
         <is>
           <t>NODE_S2006_07_0049</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -13845,6 +14175,12 @@
           <t>NODE_S2007_08_0053</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0055</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13854,6 +14190,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -13887,6 +14231,8 @@
           <t>NODE_S2007_08_0053</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13896,6 +14242,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -14018,6 +14372,12 @@
           <t>NODE_S2007_08_0057</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0060</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14032,6 +14392,14 @@
         <is>
           <t>NODE_S2006_07_0057</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -14065,6 +14433,8 @@
           <t>NODE_S2007_08_0057</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14074,6 +14444,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -14107,6 +14485,8 @@
           <t>NODE_S2007_08_0057</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14116,6 +14496,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -14149,6 +14537,12 @@
           <t>NODE_S2007_08_0057</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0060</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14158,6 +14552,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -14322,6 +14724,12 @@
           <t>NODE_S2007_08_0064</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0067</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14336,6 +14744,14 @@
         <is>
           <t>NODE_S2006_07_0064</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -14416,6 +14832,8 @@
           <t>NODE_S2007_08_0064</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14430,6 +14848,14 @@
         <is>
           <t>NODE_S2006_07_0067</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -14463,6 +14889,8 @@
           <t>NODE_S2007_08_0064</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14477,6 +14905,14 @@
         <is>
           <t>NODE_S2006_07_0067</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -14557,6 +14993,12 @@
           <t>NODE_S2007_08_0069</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0071</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14571,6 +15013,14 @@
         <is>
           <t>NODE_S2006_07_0072</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -14604,6 +15054,8 @@
           <t>NODE_S2007_08_0069</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14613,6 +15065,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -14646,6 +15106,8 @@
           <t>NODE_S2007_08_0069</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14655,6 +15117,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -14704,6 +15174,8 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -14833,6 +15305,7 @@
         </is>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>

--- a/data/S2007_08_FINAL.xlsx
+++ b/data/S2007_08_FINAL.xlsx
@@ -827,6 +827,11 @@
           <t>HC Slavia Praha (C)</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>52</v>
       </c>
@@ -11993,8 +11998,6 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12050,8 +12053,6 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12107,8 +12108,6 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12164,8 +12163,6 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12221,8 +12218,6 @@
           <t>NODE_S2007_08_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12278,8 +12273,6 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12335,8 +12328,6 @@
           <t>NODE_S2007_08_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12686,7 +12677,6 @@
           <t>NODE_S2007_08_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12747,7 +12737,6 @@
           <t>NODE_S2007_08_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12803,8 +12792,6 @@
           <t>NODE_S2007_08_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12860,8 +12847,6 @@
           <t>NODE_S2007_08_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13357,7 +13342,6 @@
           <t>NODE_S2007_08_0039</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13418,7 +13402,6 @@
           <t>NODE_S2007_08_0040</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13474,8 +13457,6 @@
           <t>NODE_S2007_08_0035</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13625,8 +13606,6 @@
           <t>NODE_S2007_08_0035</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13781,7 +13760,6 @@
           <t>NODE_S2007_08_0038</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13936,7 +13914,6 @@
           <t>NODE_S2007_08_0050</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13987,8 +13964,6 @@
           <t>NODE_S2007_08_0048</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14180,7 +14155,6 @@
           <t>NODE_S2007_08_0055</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14231,8 +14205,6 @@
           <t>NODE_S2007_08_0053</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14377,7 +14349,6 @@
           <t>NODE_S2007_08_0060</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14433,8 +14404,6 @@
           <t>NODE_S2007_08_0057</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14485,8 +14454,6 @@
           <t>NODE_S2007_08_0057</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14542,7 +14509,6 @@
           <t>NODE_S2007_08_0060</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14729,7 +14695,6 @@
           <t>NODE_S2007_08_0067</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14832,8 +14797,6 @@
           <t>NODE_S2007_08_0064</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14889,8 +14852,6 @@
           <t>NODE_S2007_08_0064</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14998,7 +14959,6 @@
           <t>NODE_S2007_08_0071</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15054,8 +15014,6 @@
           <t>NODE_S2007_08_0069</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15106,8 +15064,6 @@
           <t>NODE_S2007_08_0069</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15174,8 +15130,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -15305,7 +15259,6 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -26696,7 +26649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26876,6 +26829,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HC Slavia Praha</t>
         </is>
       </c>
     </row>

--- a/data/S2007_08_FINAL.xlsx
+++ b/data/S2007_08_FINAL.xlsx
@@ -15130,6 +15130,8 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -15259,6 +15261,7 @@
         </is>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>

--- a/data/S2007_08_FINAL.xlsx
+++ b/data/S2007_08_FINAL.xlsx
@@ -6394,7 +6394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8532,6 +8532,1085 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0074</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SB Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0074</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0196</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00231</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SKLH Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0074</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0197</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00232</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>6</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0074</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0198</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00233</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0199</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00234</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0200</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00235</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0201</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00236</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0202</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00237</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0203</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00238</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0204</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00239</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>7</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0205</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00240</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0206</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00241</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sokol Semanín</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0207</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00242</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Spartak Pelhřimov B</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0208</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00243</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Takže Čejov</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0209</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00244</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0210</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00245</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HC Pelhřimov</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0211</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00246</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Jiskra Humpolec B</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0212</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00247</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HC Buřenice</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0213</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00248</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>HC Počátky</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0214</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00249</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SK Telč B</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0215</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00250</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>9</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SK Horní Cerekev</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0216</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00251</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>10</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Slavoj Žirovnice</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0217</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00252</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>11</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>TJ Růžená</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0218</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00253</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8543,7 +9622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10280,6 +11359,1684 @@
       <c r="V32" t="inlineStr">
         <is>
           <t>SER_S2007_08_0033</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HC Blansko D</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0219</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00254</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Černá Hora</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0220</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00255</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Rájec – Jestřebí</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0221</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00256</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sokol Lysice</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0222</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00257</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Adamov</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0223</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00258</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Březina</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0224</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00259</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Letovice</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0225</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00260</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Kunštát</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0226</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00261</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>9</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sokol Sloup</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0227</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00262</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sokol Pokojovice</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0228</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00263</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0229</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00264</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0230</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00265</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou „B“</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0231</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00266</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jiskra Vladislav</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0232</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00267</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TJ Mohelno</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0233</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00268</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>WhiteStar Vizovice</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0234</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00269</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>KASMEN Uherský Brod</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0235</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00270</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Metropol Podkopná Lhota</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0236</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00271</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>HC Napajedla</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0237</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00272</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BUM Otrokovice</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0238</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00273</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>6</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Baťovka Zlín</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0239</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00274</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>7</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Rudí kohouti Zlín</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0240</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00275</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>KAS Asterix Napajedla</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0241</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00276</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Veverská Bitýška</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0242</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00277</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0243</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00278</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0244</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00279</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HC Slavkovice</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0245</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00280</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0246</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00281</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0247</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00282</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>7</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0248</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00283</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>HC Vatín</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0249</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00284</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Šerkovice</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0250</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00285</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Polná</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0251</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00286</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Měřín</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0252</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00287</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0253</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00288</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0254</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Blansko</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0255</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>TR_S2007_08_00290</t>
         </is>
       </c>
     </row>
@@ -11298,7 +14055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15287,6 +18044,97 @@
       <c r="A88" t="inlineStr">
         <is>
           <t>II.liga: Západ/Střed/Východ + 8F/QF/SF/finále.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0074</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0075</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Pardubický – Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0076</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Jihomoravský – Blansko</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>REG_JHM</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>NODE_S2007_08_0069</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -18922,7 +21770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J184"/>
+  <dimension ref="A1:J244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -26638,6 +29486,1926 @@
       <c r="J184" t="inlineStr">
         <is>
           <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0196</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SB Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SB Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0197</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SKLH Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SKLH Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0198</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0199</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0200</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0201</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0202</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0203</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0204</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0205</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0206</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0207</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Sokol Semanín</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Sokol Semanín</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0208</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Spartak Pelhřimov B</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Spartak Pelhřimov B</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0209</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Takže Čejov</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Takže Čejov</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0210</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0211</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>HC Pelhřimov</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>HC Pelhřimov</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0212</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Jiskra Humpolec B</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Jiskra Humpolec B</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0213</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>HC Buřenice</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>HC Buřenice</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0214</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>HC Počátky</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>HC Počátky</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0215</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>SK Telč B</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>SK Telč B</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0216</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SK Horní Cerekev</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SK Horní Cerekev</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0217</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Slavoj Žirovnice</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Slavoj Žirovnice</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0218</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>TJ Růžená</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>TJ Růžená</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0219</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>HC Blansko D</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>HC Blansko D</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0220</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Černá Hora</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Černá Hora</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0221</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Rájec – Jestřebí</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Rájec – Jestřebí</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0222</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Sokol Lysice</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Sokol Lysice</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0223</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Adamov</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Adamov</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0224</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Březina</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Březina</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0225</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Letovice</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Letovice</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0226</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Kunštát</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Kunštát</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0227</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Sokol Sloup</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Sokol Sloup</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0228</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Sokol Pokojovice</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Sokol Pokojovice</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0229</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0230</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0231</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou „B“</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou „B“</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0232</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Jiskra Vladislav</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Jiskra Vladislav</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0233</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>TJ Mohelno</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>TJ Mohelno</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0234</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>WhiteStar Vizovice</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>WhiteStar Vizovice</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0235</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>KASMEN Uherský Brod</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>KASMEN Uherský Brod</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0236</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Metropol Podkopná Lhota</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Metropol Podkopná Lhota</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0237</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>HC Napajedla</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>HC Napajedla</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0238</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>BUM Otrokovice</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>BUM Otrokovice</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0239</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Baťovka Zlín</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Baťovka Zlín</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0240</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Rudí kohouti Zlín</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Rudí kohouti Zlín</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0241</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>KAS Asterix Napajedla</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>KAS Asterix Napajedla</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0242</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Veverská Bitýška</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Veverská Bitýška</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0243</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0244</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0245</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>HC Slavkovice</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>HC Slavkovice</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0246</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0247</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0248</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0249</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>HC Vatín</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>HC Vatín</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0250</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Šerkovice</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Šerkovice</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0251</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Polná</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Polná</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0252</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Měřín</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Měřín</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0253</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0254</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CLUB_S2007_08_0255</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
         </is>
       </c>
     </row>

--- a/data/S2007_08_FINAL.xlsx
+++ b/data/S2007_08_FINAL.xlsx
@@ -17887,8 +17887,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -18018,7 +18016,6 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -34179,7 +34176,7 @@
           <t>CLUB_S2007_08_0007</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34199,7 +34196,7 @@
           <t>CLUB_S2007_08_0016</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34219,7 +34216,7 @@
           <t>CLUB_S2007_08_0019</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34239,7 +34236,7 @@
           <t>CLUB_S2007_08_0033</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34259,7 +34256,7 @@
           <t>CLUB_S2007_08_0053</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2006_07_0135 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -34279,7 +34276,7 @@
           <t>CLUB_S2007_08_0054</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -34299,7 +34296,7 @@
           <t>CLUB_S2007_08_0057</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34319,7 +34316,7 @@
           <t>CLUB_S2007_08_0064</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34339,7 +34336,7 @@
           <t>CLUB_S2007_08_0069</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'Hockey Club Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34359,7 +34356,7 @@
           <t>CLUB_S2007_08_0071</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34379,7 +34376,7 @@
           <t>CLUB_S2007_08_0075</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34399,7 +34396,7 @@
           <t>CLUB_S2007_08_0109</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34419,7 +34416,7 @@
           <t>CLUB_S2007_08_0123</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -34439,7 +34436,7 @@
           <t>CLUB_S2007_08_0134</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34459,7 +34456,7 @@
           <t>CLUB_S2007_08_0145</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -34479,7 +34476,7 @@
           <t>CLUB_S2007_08_0147</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34499,7 +34496,7 @@
           <t>CLUB_S2007_08_0153</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34519,7 +34516,7 @@
           <t>CLUB_S2007_08_0160</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34539,7 +34536,7 @@
           <t>CLUB_S2007_08_0162</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -34559,7 +34556,7 @@
           <t>CLUB_S2007_08_0174</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -34579,7 +34576,7 @@
           <t>CLUB_S2007_08_0187</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34599,7 +34596,7 @@
           <t>NODE_S2007_08_0030</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
@@ -34619,7 +34616,7 @@
           <t>NODE_S2007_08_0031</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>

--- a/data/S2007_08_FINAL.xlsx
+++ b/data/S2007_08_FINAL.xlsx
@@ -15735,7 +15735,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KVAL  skupina A</t>
+          <t>KVAL skupina A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -15767,7 +15767,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KVAL  skupina B</t>
+          <t>KVAL skupina B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -15846,7 +15846,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -16549,7 +16549,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -16643,7 +16643,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Finále</t>
+          <t>Jihočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40</t>
+          <t>Ústecký-Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40 základní část</t>
+          <t>Ústecký-Karlovarský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 základní část</t>
+          <t>Liberecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 Finále</t>
+          <t>Liberecký, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -17036,7 +17036,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 základní část</t>
+          <t>Hradecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina o 5.- 8.místo</t>
+          <t>Hradecký, 4. úroveň, skupina o 5.- 8.místo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -17188,7 +17188,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 Finále</t>
+          <t>Hradecký, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 základní část</t>
+          <t>Hradecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina A</t>
+          <t>Hradecký, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina B</t>
+          <t>Hradecký, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 základní část</t>
+          <t>Pardubický, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -17484,7 +17484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina B</t>
+          <t>Pardubický, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -17641,7 +17641,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 základní část</t>
+          <t>Jihomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -17748,7 +17748,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -17848,7 +17848,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -17887,6 +17887,8 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -17919,7 +17921,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -18016,6 +18018,7 @@
         </is>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>

--- a/data/S2007_08_FINAL.xlsx
+++ b/data/S2007_08_FINAL.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -17887,8 +17887,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -18018,7 +18016,6 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -32354,7 +32351,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -32437,7 +32434,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -32983,7 +32980,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -33061,7 +33058,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
